--- a/NHIS variable list_Modified_new.xlsx
+++ b/NHIS variable list_Modified_new.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hrmor\OneDrive - North Carolina A&amp;T State University\06_Codes\NHIS-surf\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ncaandt-my.sharepoint.com/personal/hmoradi_ncat_edu/Documents/06_Codes/NHIS-surf/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4290F889-0693-4DB9-9F9C-BB9399D5CECC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="62" documentId="8_{D5C0F2D8-590C-5543-A8E4-295500E93607}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B328F89D-B2B4-407D-9ACB-49FA81B63142}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{AA949552-4F9F-40F0-90AF-3F34A678AD64}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{AA949552-4F9F-40F0-90AF-3F34A678AD64}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="183">
   <si>
     <t>description</t>
   </si>
@@ -575,9 +575,6 @@
   </si>
   <si>
     <t>Labels: Northeast Region of U.S.; Midwest Region of U.S.; Southern Region of U.S.; Western Region of U.S.</t>
-  </si>
-  <si>
-    <t>HHX</t>
   </si>
 </sst>
 </file>
@@ -677,7 +674,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -700,7 +697,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1015,7 +1011,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C15A277-6A4B-4FED-94DF-816CADB374AA}">
-  <dimension ref="B1:J64"/>
+  <dimension ref="B1:J63"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -2227,11 +2223,6 @@
         <v>74</v>
       </c>
     </row>
-    <row r="64" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B64" s="14" t="s">
-        <v>183</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/NHIS variable list_Modified_new.xlsx
+++ b/NHIS variable list_Modified_new.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ncaandt-my.sharepoint.com/personal/hmoradi_ncat_edu/Documents/06_Codes/NHIS-surf/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hrmor\OneDrive - North Carolina A&amp;T State University\06_Codes\NHIS-surf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="62" documentId="8_{D5C0F2D8-590C-5543-A8E4-295500E93607}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B328F89D-B2B4-407D-9ACB-49FA81B63142}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4290F889-0693-4DB9-9F9C-BB9399D5CECC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{AA949552-4F9F-40F0-90AF-3F34A678AD64}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{AA949552-4F9F-40F0-90AF-3F34A678AD64}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="184">
   <si>
     <t>description</t>
   </si>
@@ -575,6 +575,9 @@
   </si>
   <si>
     <t>Labels: Northeast Region of U.S.; Midwest Region of U.S.; Southern Region of U.S.; Western Region of U.S.</t>
+  </si>
+  <si>
+    <t>HHX</t>
   </si>
 </sst>
 </file>
@@ -674,7 +677,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -697,6 +700,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1011,7 +1015,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C15A277-6A4B-4FED-94DF-816CADB374AA}">
-  <dimension ref="B1:J63"/>
+  <dimension ref="B1:J64"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -2223,6 +2227,11 @@
         <v>74</v>
       </c>
     </row>
+    <row r="64" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B64" s="14" t="s">
+        <v>183</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
